--- a/data/trans_camb/P43C-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P43C-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,02</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,02</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1,33</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,5; 14,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,19; 12,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,1; 7,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 14,53</t>
+          <t>1,5; 14,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 11,79</t>
+          <t>-1,19; 12,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 8,17</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 14,53</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-1,44; 11,79</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-5,33; 8,17</t>
+          <t>-6,1; 7,51</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,88; 21,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,55; 17,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,72; 10,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 20,86</t>
+          <t>1,88; 21,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 16,88</t>
+          <t>-1,55; 17,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 11,68</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,85; 20,86</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 16,88</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-7,04; 11,68</t>
+          <t>-7,72; 10,75</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,03</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,72</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,85</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,85</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,03</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13,72</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>7,85</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,4; 20,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,22; 20,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,92; 14,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 20,06</t>
+          <t>7,4; 20,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 19,97</t>
+          <t>7,22; 20,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 14,56</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 20,06</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7,57; 19,97</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 14,56</t>
+          <t>0,92; 14,24</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20,26%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11,58%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,65; 30,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,05; 31,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,18; 22,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,72; 31,62</t>
+          <t>10,65; 30,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 31,37</t>
+          <t>10,05; 31,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 22,92</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,72; 31,62</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10,82; 31,37</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2,13; 22,92</t>
+          <t>1,18; 22,31</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,19</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,96</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,01</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-3,01</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>6,96</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>-3,01</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,01; 12,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,22; 18,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,16; 7,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 12,79</t>
+          <t>-6,01; 12,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 17,26</t>
+          <t>-3,22; 18,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 7,63</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 12,79</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-2,88; 17,26</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-12,42; 7,63</t>
+          <t>-14,16; 7,7</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,63%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-4,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>-4,63%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,51; 20,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,73; 30,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-19,92; 13,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 21,82</t>
+          <t>-8,51; 20,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 28,6</t>
+          <t>-4,73; 30,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 13,0</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-7,89; 21,82</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-4,08; 28,6</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-17,8; 13,0</t>
+          <t>-19,92; 13,25</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,55</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9,33</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-9,33</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,9</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13,55</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>-9,33</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,1; 21,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,73; 18,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-38,12; 9,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,65; 20,64</t>
+          <t>11,1; 21,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,33; 18,61</t>
+          <t>8,73; 18,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 9,96</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,65; 20,64</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>8,33; 18,61</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-35,47; 9,96</t>
+          <t>-38,12; 9,47</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-16,49%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-16,49%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>28,1%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>23,95%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>-16,49%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,91; 39,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,78; 34,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,29; 17,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,22; 38,65</t>
+          <t>18,91; 39,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,05; 34,99</t>
+          <t>14,78; 34,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,5; 18,04</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>18,22; 38,65</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14,05; 34,99</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-62,5; 18,04</t>
+          <t>-66,29; 17,01</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,17</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8,17</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>6,21</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>4,15</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,46; 13,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,29; 12,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,22; 16,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,84; 13,72</t>
+          <t>2,46; 13,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 11,65</t>
+          <t>0,29; 12,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 17,52</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1,84; 13,72</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 11,65</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-3,77; 17,52</t>
+          <t>-4,22; 16,22</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>7,44%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,02; 26,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,65; 23,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,38; 30,41</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2,95; 26,3</t>
+          <t>4,02; 26,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,91; 22,88</t>
+          <t>0,65; 23,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 32,21</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2,95; 26,3</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0,91; 22,88</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>-6,97; 32,21</t>
+          <t>-7,38; 30,41</t>
         </is>
       </c>
     </row>
@@ -1704,17 +1376,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,65</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1728,21 +1400,6 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>9,65</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>7,64</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>2,33</t>
         </is>
@@ -1757,47 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,52; 13,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,29; 12,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,22; 7,12</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,28; 13,67</t>
+          <t>5,52; 13,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,55</t>
+          <t>3,29; 12,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 7,05</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,28; 13,67</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3,21; 11,55</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>-2,18; 7,05</t>
+          <t>-2,22; 7,12</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1452,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1834,21 +1476,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>23,74%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
         </is>
@@ -1863,47 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,03; 35,32</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,83; 31,73</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,31; 18,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12,76; 34,96</t>
+          <t>13,03; 35,32</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,3; 29,57</t>
+          <t>7,83; 31,73</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 18,2</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>12,76; 34,96</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>7,3; 29,57</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>-5,12; 18,2</t>
+          <t>-5,31; 18,35</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1532,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,32</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1944,21 +1556,6 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>11,32</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>10,13</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2,19</t>
         </is>
@@ -1973,47 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,84; 13,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,69; 12,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,38; 7,77</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,98; 13,43</t>
+          <t>8,84; 13,43</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,74</t>
+          <t>7,69; 12,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 8,32</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>8,98; 13,43</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>7,96; 12,74</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-9,51; 8,32</t>
+          <t>-9,38; 7,77</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1608,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2050,21 +1632,6 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>18,84%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>4,08%</t>
         </is>
@@ -2079,47 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,09; 25,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,95; 23,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,75; 14,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16,5; 25,89</t>
+          <t>16,09; 25,49</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,46; 24,27</t>
+          <t>13,95; 23,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 15,62</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>16,5; 25,89</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>14,46; 24,27</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>-17,61; 15,62</t>
+          <t>-17,75; 14,45</t>
         </is>
       </c>
     </row>
@@ -2131,13 +1683,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/P43C-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P43C-Clase-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 14,58</t>
+          <t>0,38; 14,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 12,17</t>
+          <t>-1,7; 11,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 7,51</t>
+          <t>-6,31; 6,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 14,58</t>
+          <t>0,38; 14,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 12,17</t>
+          <t>-1,7; 11,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 7,51</t>
+          <t>-6,31; 6,8</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 21,14</t>
+          <t>0,49; 20,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 17,43</t>
+          <t>-2,1; 17,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 10,75</t>
+          <t>-8,17; 9,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 21,14</t>
+          <t>0,49; 20,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 17,43</t>
+          <t>-2,1; 17,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 10,75</t>
+          <t>-8,17; 9,84</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,85</t>
+          <t>7,08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,85</t>
+          <t>7,08</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 20,0</t>
+          <t>6,83; 20,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 20,15</t>
+          <t>6,46; 19,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 14,24</t>
+          <t>0,67; 13,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 20,0</t>
+          <t>6,83; 20,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 20,15</t>
+          <t>6,46; 19,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 14,24</t>
+          <t>0,67; 13,82</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 30,96</t>
+          <t>9,75; 31,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 31,26</t>
+          <t>9,3; 29,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 22,31</t>
+          <t>0,88; 21,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 30,96</t>
+          <t>9,75; 31,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 31,26</t>
+          <t>9,3; 29,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 22,31</t>
+          <t>0,88; 21,7</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>-3,3</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>-3,3</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 12,24</t>
+          <t>-5,71; 14,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 18,12</t>
+          <t>-3,77; 18,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 7,7</t>
+          <t>-13,72; 7,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 12,24</t>
+          <t>-5,71; 14,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 18,12</t>
+          <t>-3,77; 18,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 7,7</t>
+          <t>-13,72; 7,13</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-4,63%</t>
+          <t>-5,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-4,63%</t>
+          <t>-5,06%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 20,26</t>
+          <t>-8,35; 23,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 30,91</t>
+          <t>-5,34; 30,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 13,25</t>
+          <t>-19,84; 11,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 20,26</t>
+          <t>-8,35; 23,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 30,91</t>
+          <t>-5,34; 30,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 13,25</t>
+          <t>-19,84; 11,82</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,33</t>
+          <t>7,88</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,33</t>
+          <t>7,88</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,1; 21,05</t>
+          <t>11,24; 20,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,73; 18,54</t>
+          <t>8,2; 18,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 9,47</t>
+          <t>2,85; 12,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,1; 21,05</t>
+          <t>11,24; 20,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,73; 18,54</t>
+          <t>8,2; 18,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 9,47</t>
+          <t>2,85; 12,95</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-16,49%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-16,49%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,91; 39,65</t>
+          <t>18,65; 38,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,78; 34,69</t>
+          <t>13,65; 33,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 17,01</t>
+          <t>4,78; 24,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,91; 39,65</t>
+          <t>18,65; 38,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,78; 34,69</t>
+          <t>13,65; 33,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 17,01</t>
+          <t>4,78; 24,13</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>-4,72</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>-4,72</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 13,88</t>
+          <t>2,73; 13,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 12,05</t>
+          <t>0,97; 12,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 16,22</t>
+          <t>-9,79; 0,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 13,88</t>
+          <t>2,73; 13,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 12,05</t>
+          <t>0,97; 12,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 16,22</t>
+          <t>-9,79; 0,94</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>-8,46%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>-8,46%</t>
         </is>
       </c>
     </row>
@@ -1334,39 +1334,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4,02; 26,35</t>
+          <t>4,66; 26,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,65; 23,15</t>
+          <t>1,41; 23,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 30,41</t>
+          <t>-16,53; 1,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,02; 26,35</t>
+          <t>4,66; 26,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,65; 23,15</t>
+          <t>1,41; 23,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 30,41</t>
+          <t>-16,53; 1,82</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>1,45</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,58</t>
+          <t>5,57; 13,5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,29</t>
+          <t>3,65; 12,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 7,12</t>
+          <t>-2,95; 6,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,58</t>
+          <t>5,57; 13,5</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,29</t>
+          <t>3,65; 12,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 7,12</t>
+          <t>-2,95; 6,33</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13,03; 35,32</t>
+          <t>13,09; 35,14</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7,83; 31,73</t>
+          <t>8,74; 30,76</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 18,35</t>
+          <t>-6,86; 16,12</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13,03; 35,32</t>
+          <t>13,09; 35,14</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,83; 31,73</t>
+          <t>8,74; 30,76</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 18,35</t>
+          <t>-6,86; 16,12</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>4,18</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,43</t>
+          <t>8,74; 13,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,49</t>
+          <t>7,7; 12,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 7,77</t>
+          <t>1,68; 6,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,43</t>
+          <t>8,74; 13,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,49</t>
+          <t>7,7; 12,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 7,77</t>
+          <t>1,68; 6,41</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>16,09; 25,49</t>
+          <t>15,9; 25,86</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13,95; 23,68</t>
+          <t>13,88; 23,74</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 14,45</t>
+          <t>3,08; 12,31</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16,09; 25,49</t>
+          <t>15,9; 25,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>13,95; 23,68</t>
+          <t>13,88; 23,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 14,45</t>
+          <t>3,08; 12,31</t>
         </is>
       </c>
     </row>
